--- a/artfynd/S 264-2026 artfynd.xlsx
+++ b/artfynd/S 264-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604202</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604222</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604221</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604207</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604230</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389029</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389032</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389033</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389034</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389035</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389036</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1992,6 +2057,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389037</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,6 +2164,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389038</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2196,6 +2271,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389039</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,6 +2378,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389040</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2400,6 +2485,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389041</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2501,6 +2591,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604208</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2602,6 +2697,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604210</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2703,6 +2803,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604212</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2804,6 +2909,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604201</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2905,6 +3015,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604216</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3006,6 +3121,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604226</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3107,6 +3227,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604237</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3208,6 +3333,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604213</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3314,6 +3444,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89604227</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3416,6 +3551,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389001</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3518,6 +3658,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389002</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3620,6 +3765,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389003</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3722,6 +3872,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389004</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3824,6 +3979,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389005</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3926,6 +4086,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389007</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4028,6 +4193,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389008</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4130,6 +4300,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389009</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4232,6 +4407,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389010</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4334,6 +4514,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389011</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4436,6 +4621,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389012</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4546,6 +4736,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131389013</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4639,8 +4834,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5954791</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>